--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,10 +483,8 @@
           <t>Project A</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="D2" t="n">
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -500,14 +498,184 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7 days</t>
+          <t>6 days</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>46174.54501139747</v>
+        <v>46174.59906916667</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>b876557e-07c3-46cd-bcde-0a561c2bb36c</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Project A</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Jeanie</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ITP</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3 days</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>53</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>46174.5480568287</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>117c61d7-7a1f-4d14-86c7-e406d56bc08b</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Project A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>sona</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sona</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3 days</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>46174.62240327546</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>a99b94fe-76ef-4e70-ad11-6c6cc14d6bf4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Project A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sona</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ITP</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2 days</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>41</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>46174.624611875</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>40edadd2-2ffb-4a05-8915-98f6c5c3628a</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Project A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Logan</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3 days</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>75</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>46174.62928832823</v>
       </c>
     </row>
   </sheetData>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6 +465,160 @@
         <is>
           <t>Last Updated</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>fe6d9da5-e2f0-4524-9e0b-0e55025c8459</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Requirement Document</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>46174.602025625</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>f4db8073-4f75-492a-996e-011238f233b6</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sfw</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ffwe</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Requirement Document</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>46174.60209714121</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>e172cbff-53b4-484c-a10d-bdce007d1b9b</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>rish</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Requirement Document</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>10 days</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>46174.60430481481</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>53d21ad2-b8f4-4c4e-84ef-c5636b689c0f</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sona</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Requirement Document</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>70</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>46174.60456082991</v>
       </c>
     </row>
   </sheetData>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,7 +618,50 @@
         <v>70</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>46174.60456082991</v>
+        <v>46174.60456083333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>a7f50a74-a839-4f15-b692-cc445036c2a4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sona</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10 days</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>22</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>46175.50705595598</v>
       </c>
     </row>
   </sheetData>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -417,51 +417,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Record ID</t>
+          <t>Project_ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Project ID</t>
+          <t>Project_Name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Project Name</t>
+          <t>Employee_Name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Employee ID</t>
+          <t>Project_Type</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>Project_Team</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Job Undertaken</t>
+          <t>Job_Undertaken</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Time Duration</t>
+          <t>Job_Status</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
+        <is>
+          <t>Start_Date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>End_Date</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
@@ -470,152 +480,174 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ffa6f712-a531-48c0-a8e8-3298c9cb2a05</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>Project 2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Project A</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>16</v>
+          <t>Rue</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Frankie</t>
+          <t>SVAT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Requirement Document</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6 days</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>38</v>
+          <t>WIP</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>46174.59906916667</v>
-      </c>
+        <v>46165</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>b876557e-07c3-46cd-bcde-0a561c2bb36c</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>Project 3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Project A</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>23</v>
+          <t>Cassie</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In-house</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeanie</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ITP</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3 days</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>53</v>
+          <t>YTP</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>46174.5480568287</v>
-      </c>
+        <v>46159</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>117c61d7-7a1f-4d14-86c7-e406d56bc08b</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>Project 2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Project A</t>
+          <t>Fezco</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sona</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sona</t>
+          <t>SVAT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Requirements Document</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3 days</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>25</v>
+          <t>WIP</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>VBA</t>
+        </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>46174.62240327546</v>
-      </c>
+        <v>46142</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a99b94fe-76ef-4e70-ad11-6c6cc14d6bf4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>Project 3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Project A</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>In-house</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sona</t>
+          <t>ADAS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -625,58 +657,266 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2 days</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>41</v>
+          <t>YTP</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>46174.624611875</v>
-      </c>
+        <v>46138</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>40edadd2-2ffb-4a05-8915-98f6c5c3628a</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>Project 3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Project A</t>
+          <t>Maddy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>In-house</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>SVAT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>46131</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Project 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Laurie</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In-house</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PMO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Design Document</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>WIP</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>VBA</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Project 3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Faye</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In-house</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SVAT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ITP</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>YTP</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>VBA</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Project 3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wayne</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ADAS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Project 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ADAS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Coding</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3 days</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>75</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>46174.62928832823</v>
-      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
